--- a/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 92 D20 Spring 2024 24GE03I94 Zoop.xlsx
+++ b/data/raw/GLNPO 2024 Spring/Erie/D20/Zoops/ER 92 D20 Spring 2024 24GE03I94 Zoop.xlsx
@@ -1,26 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cmars\OneDrive\Desktop\CCM Work Files\GLNPO Zooplankton Database\data\raw\GLNPO 2024 Spring\Erie\D20\Zoops\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90B5F503-3C83-4514-905E-4030391AD9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E09DDA57-4E50-4ACE-8F42-91219799F6B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6900" yWindow="1470" windowWidth="21600" windowHeight="11280" xr2:uid="{826C57E6-8BA3-4AC1-9B33-AF4591DE6347}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{826C57E6-8BA3-4AC1-9B33-AF4591DE6347}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$245</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$R$246</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <pivotCaches>
-    <pivotCache cacheId="19" r:id="rId2"/>
+    <pivotCache cacheId="21" r:id="rId2"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3029" uniqueCount="97">
   <si>
     <t>SAMPLENUM</t>
   </si>
@@ -234,9 +234,6 @@
   </si>
   <si>
     <t>LIMCOPE</t>
-  </si>
-  <si>
-    <t>CALIM</t>
   </si>
   <si>
     <t>Limnocalanus macrurus</t>
@@ -5599,7 +5596,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C592F0B1-84C2-477D-965D-46A5BCCD4F36}" name="PivotTable2" cacheId="19" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{C592F0B1-84C2-477D-965D-46A5BCCD4F36}" name="PivotTable2" cacheId="21" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0">
   <location ref="T5:X27" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="18">
     <pivotField showAll="0"/>
@@ -6070,20 +6067,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF56A237-F653-4A4F-8F36-04017A650C5F}">
   <dimension ref="A1:X246"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="24.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="10.44140625" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="29" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="16.42578125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="11.28515625" customWidth="1"/>
-    <col min="23" max="23" width="2.28515625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="11.33203125" customWidth="1"/>
+    <col min="23" max="23" width="2.33203125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6139,7 +6136,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -6192,7 +6189,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -6245,7 +6242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -6298,7 +6295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -6351,13 +6348,13 @@
         <v>1</v>
       </c>
       <c r="T5" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="U5" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="U5" s="11" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -6410,22 +6407,22 @@
         <v>1</v>
       </c>
       <c r="T6" s="11" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="U6" t="s">
         <v>21</v>
       </c>
       <c r="V6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="W6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="X6" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -6493,7 +6490,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -6558,7 +6555,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -6623,7 +6620,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -6676,7 +6673,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="12" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="U10">
         <v>1</v>
@@ -6688,7 +6685,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -6753,7 +6750,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -6818,7 +6815,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -6880,7 +6877,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -6933,7 +6930,7 @@
         <v>1</v>
       </c>
       <c r="T14" s="12" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="U14">
         <v>1</v>
@@ -6945,7 +6942,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -7010,7 +7007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -7075,7 +7072,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7128,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="12" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="U17">
         <v>2</v>
@@ -7140,7 +7137,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -7193,7 +7190,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="12" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="U18">
         <v>0</v>
@@ -7208,7 +7205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>18</v>
       </c>
@@ -7273,7 +7270,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -7335,7 +7332,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="21" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -7400,7 +7397,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -7465,7 +7462,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="23" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>18</v>
       </c>
@@ -7518,7 +7515,7 @@
         <v>1</v>
       </c>
       <c r="T23" s="12" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="U23">
         <v>1</v>
@@ -7533,7 +7530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -7586,7 +7583,7 @@
         <v>1</v>
       </c>
       <c r="T24" s="12" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="U24">
         <v>1</v>
@@ -7598,7 +7595,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -7663,7 +7660,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="26" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -7716,7 +7713,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="12" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U26">
         <v>0</v>
@@ -7728,7 +7725,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -7781,7 +7778,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="12" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="U27">
         <v>168</v>
@@ -7796,7 +7793,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="28" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -7849,7 +7846,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -7902,7 +7899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -7955,16 +7952,16 @@
         <v>1</v>
       </c>
       <c r="T30" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="U30" s="14" t="s">
         <v>90</v>
-      </c>
-      <c r="U30" s="14" t="s">
-        <v>91</v>
       </c>
       <c r="V30" s="15">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="31" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -8018,13 +8015,13 @@
       </c>
       <c r="T31" s="16"/>
       <c r="U31" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V31" s="15">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="32" spans="1:24" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -8077,16 +8074,16 @@
         <v>1</v>
       </c>
       <c r="T32" s="13" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="U32" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V32" s="15">
         <v>1.0009999999999999</v>
       </c>
     </row>
-    <row r="33" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -8140,13 +8137,13 @@
       </c>
       <c r="T33" s="16"/>
       <c r="U33" s="14" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="V33" s="15">
         <v>1.0029999999999999</v>
       </c>
     </row>
-    <row r="34" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -8199,14 +8196,14 @@
         <v>1</v>
       </c>
       <c r="T34" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="U34" s="18" t="s">
         <v>93</v>
       </c>
-      <c r="U34" s="18" t="s">
-        <v>94</v>
-      </c>
       <c r="V34" s="19"/>
     </row>
-    <row r="35" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -8259,14 +8256,14 @@
         <v>1</v>
       </c>
       <c r="T35" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="U35" s="18" t="s">
         <v>95</v>
       </c>
-      <c r="U35" s="18" t="s">
-        <v>96</v>
-      </c>
       <c r="V35" s="19"/>
     </row>
-    <row r="36" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -8319,12 +8316,12 @@
         <v>1</v>
       </c>
       <c r="T36" s="14" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="U36" s="18"/>
       <c r="V36" s="19"/>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -8377,7 +8374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -8430,7 +8427,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -8483,7 +8480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -8536,7 +8533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -8589,7 +8586,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -8642,7 +8639,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -8695,7 +8692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -8733,7 +8730,7 @@
         <v>63</v>
       </c>
       <c r="M44" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N44" t="s">
         <v>28</v>
@@ -8748,7 +8745,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -8801,7 +8798,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:22" ht="30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -8839,7 +8836,7 @@
         <v>63</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N46" t="s">
         <v>28</v>
@@ -8854,7 +8851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -8907,7 +8904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -8960,7 +8957,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -9013,7 +9010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -9066,7 +9063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -9119,7 +9116,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -9172,7 +9169,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -9225,7 +9222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -9278,7 +9275,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -9331,7 +9328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -9384,7 +9381,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -9437,7 +9434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -9490,7 +9487,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -9543,7 +9540,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -9596,7 +9593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -9649,7 +9646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -9702,7 +9699,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>18</v>
       </c>
@@ -9755,7 +9752,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -9808,7 +9805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>18</v>
       </c>
@@ -9861,7 +9858,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -9914,7 +9911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -9952,7 +9949,7 @@
         <v>63</v>
       </c>
       <c r="M67" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N67" t="s">
         <v>28</v>
@@ -9967,7 +9964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -10020,7 +10017,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -10052,10 +10049,10 @@
         <v>24</v>
       </c>
       <c r="K69" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="M69" s="4" t="s">
         <v>39</v>
@@ -10073,7 +10070,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -10111,7 +10108,7 @@
         <v>63</v>
       </c>
       <c r="M70" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N70" t="s">
         <v>28</v>
@@ -10126,7 +10123,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -10179,7 +10176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -10232,7 +10229,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -10285,7 +10282,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -10338,7 +10335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -10391,7 +10388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>18</v>
       </c>
@@ -10444,7 +10441,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -10497,7 +10494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -10535,7 +10532,7 @@
         <v>63</v>
       </c>
       <c r="M78" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N78" t="s">
         <v>28</v>
@@ -10550,7 +10547,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -10603,7 +10600,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -10656,7 +10653,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -10709,7 +10706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>18</v>
       </c>
@@ -10762,7 +10759,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>18</v>
       </c>
@@ -10815,7 +10812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -10868,7 +10865,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -10921,7 +10918,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -10974,7 +10971,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -11027,7 +11024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>18</v>
       </c>
@@ -11080,7 +11077,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>18</v>
       </c>
@@ -11133,7 +11130,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>18</v>
       </c>
@@ -11186,7 +11183,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -11239,7 +11236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -11292,7 +11289,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -11345,7 +11342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -11398,7 +11395,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -11451,7 +11448,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -11504,7 +11501,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -11557,7 +11554,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -11595,7 +11592,7 @@
         <v>63</v>
       </c>
       <c r="M98" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N98" t="s">
         <v>28</v>
@@ -11610,7 +11607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -11663,7 +11660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -11716,7 +11713,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -11769,7 +11766,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -11822,7 +11819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -11875,7 +11872,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -11928,7 +11925,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -11960,10 +11957,10 @@
         <v>24</v>
       </c>
       <c r="K105" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="L105" s="3" t="s">
         <v>83</v>
-      </c>
-      <c r="L105" s="3" t="s">
-        <v>84</v>
       </c>
       <c r="M105" t="s">
         <v>52</v>
@@ -11981,10 +11978,10 @@
         <v>1</v>
       </c>
       <c r="R105" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.25">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -12037,7 +12034,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -12090,7 +12087,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -12143,7 +12140,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -12196,7 +12193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -12234,7 +12231,7 @@
         <v>63</v>
       </c>
       <c r="M110" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N110" t="s">
         <v>28</v>
@@ -12249,7 +12246,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -12302,7 +12299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="112" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -12340,7 +12337,7 @@
         <v>63</v>
       </c>
       <c r="M112" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N112" t="s">
         <v>28</v>
@@ -12355,7 +12352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -12408,7 +12405,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -12461,7 +12458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -12514,7 +12511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -12567,7 +12564,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -12620,7 +12617,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -12673,7 +12670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -12726,7 +12723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -12779,7 +12776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -12811,10 +12808,10 @@
         <v>24</v>
       </c>
       <c r="K121" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L121" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="L121" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="M121" s="4" t="s">
         <v>57</v>
@@ -12832,10 +12829,10 @@
         <v>1</v>
       </c>
       <c r="R121" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -12888,7 +12885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -12920,10 +12917,10 @@
         <v>24</v>
       </c>
       <c r="K123" t="s">
+        <v>69</v>
+      </c>
+      <c r="L123" t="s">
         <v>70</v>
-      </c>
-      <c r="L123" t="s">
-        <v>71</v>
       </c>
       <c r="M123" t="s">
         <v>32</v>
@@ -12941,7 +12938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -12994,7 +12991,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -13047,7 +13044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -13100,7 +13097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -13132,10 +13129,10 @@
         <v>24</v>
       </c>
       <c r="K127" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L127" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="L127" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="M127" s="4" t="s">
         <v>57</v>
@@ -13153,10 +13150,10 @@
         <v>1</v>
       </c>
       <c r="R127" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -13209,7 +13206,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -13262,7 +13259,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -13315,7 +13312,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -13368,7 +13365,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -13421,7 +13418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -13474,7 +13471,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -13506,10 +13503,10 @@
         <v>24</v>
       </c>
       <c r="K134" t="s">
+        <v>72</v>
+      </c>
+      <c r="L134" t="s">
         <v>73</v>
-      </c>
-      <c r="L134" t="s">
-        <v>74</v>
       </c>
       <c r="M134" t="s">
         <v>35</v>
@@ -13527,7 +13524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -13580,7 +13577,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -13633,7 +13630,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -13671,7 +13668,7 @@
         <v>63</v>
       </c>
       <c r="M137" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N137" t="s">
         <v>28</v>
@@ -13686,7 +13683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -13739,7 +13736,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -13792,7 +13789,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -13845,7 +13842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -13883,7 +13880,7 @@
         <v>63</v>
       </c>
       <c r="M141" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N141" t="s">
         <v>28</v>
@@ -13898,7 +13895,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -13951,7 +13948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -14004,7 +14001,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -14057,7 +14054,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -14110,7 +14107,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>18</v>
       </c>
@@ -14163,7 +14160,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -14216,7 +14213,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -14230,7 +14227,7 @@
         <v>-1</v>
       </c>
       <c r="E148" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F148">
         <v>16</v>
@@ -14269,7 +14266,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -14283,7 +14280,7 @@
         <v>-1</v>
       </c>
       <c r="E149" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F149">
         <v>16</v>
@@ -14322,7 +14319,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -14336,7 +14333,7 @@
         <v>-1</v>
       </c>
       <c r="E150" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F150">
         <v>16</v>
@@ -14375,7 +14372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -14389,7 +14386,7 @@
         <v>-1</v>
       </c>
       <c r="E151" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F151">
         <v>16</v>
@@ -14428,7 +14425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -14442,7 +14439,7 @@
         <v>-1</v>
       </c>
       <c r="E152" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F152">
         <v>16</v>
@@ -14481,7 +14478,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -14495,7 +14492,7 @@
         <v>-1</v>
       </c>
       <c r="E153" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F153">
         <v>16</v>
@@ -14534,7 +14531,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -14548,7 +14545,7 @@
         <v>-1</v>
       </c>
       <c r="E154" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F154">
         <v>16</v>
@@ -14587,7 +14584,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -14601,7 +14598,7 @@
         <v>-1</v>
       </c>
       <c r="E155" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F155">
         <v>16</v>
@@ -14640,7 +14637,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -14654,7 +14651,7 @@
         <v>-1</v>
       </c>
       <c r="E156" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F156">
         <v>16</v>
@@ -14693,7 +14690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -14707,7 +14704,7 @@
         <v>-1</v>
       </c>
       <c r="E157" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F157">
         <v>16</v>
@@ -14746,7 +14743,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -14760,7 +14757,7 @@
         <v>-1</v>
       </c>
       <c r="E158" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F158">
         <v>16</v>
@@ -14799,7 +14796,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -14813,7 +14810,7 @@
         <v>-1</v>
       </c>
       <c r="E159" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F159">
         <v>16</v>
@@ -14852,7 +14849,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -14866,7 +14863,7 @@
         <v>-1</v>
       </c>
       <c r="E160" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F160">
         <v>16</v>
@@ -14905,7 +14902,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -14919,7 +14916,7 @@
         <v>-1</v>
       </c>
       <c r="E161" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F161">
         <v>16</v>
@@ -14958,7 +14955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -14972,7 +14969,7 @@
         <v>-1</v>
       </c>
       <c r="E162" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F162">
         <v>16</v>
@@ -15011,7 +15008,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -15025,7 +15022,7 @@
         <v>-1</v>
       </c>
       <c r="E163" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F163">
         <v>16</v>
@@ -15064,7 +15061,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -15078,7 +15075,7 @@
         <v>-1</v>
       </c>
       <c r="E164" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F164">
         <v>16</v>
@@ -15096,10 +15093,10 @@
         <v>24</v>
       </c>
       <c r="K164" t="s">
+        <v>72</v>
+      </c>
+      <c r="L164" t="s">
         <v>73</v>
-      </c>
-      <c r="L164" t="s">
-        <v>74</v>
       </c>
       <c r="M164" t="s">
         <v>35</v>
@@ -15117,7 +15114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -15131,7 +15128,7 @@
         <v>-1</v>
       </c>
       <c r="E165" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F165">
         <v>16</v>
@@ -15170,7 +15167,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -15184,7 +15181,7 @@
         <v>-1</v>
       </c>
       <c r="E166" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F166">
         <v>16</v>
@@ -15223,7 +15220,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -15237,7 +15234,7 @@
         <v>-1</v>
       </c>
       <c r="E167" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F167">
         <v>16</v>
@@ -15276,7 +15273,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -15290,7 +15287,7 @@
         <v>-1</v>
       </c>
       <c r="E168" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F168">
         <v>16</v>
@@ -15329,7 +15326,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>18</v>
       </c>
@@ -15343,7 +15340,7 @@
         <v>-1</v>
       </c>
       <c r="E169" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F169">
         <v>16</v>
@@ -15382,7 +15379,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="170" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -15396,7 +15393,7 @@
         <v>-1</v>
       </c>
       <c r="E170" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F170">
         <v>16</v>
@@ -15420,7 +15417,7 @@
         <v>63</v>
       </c>
       <c r="M170" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N170" t="s">
         <v>28</v>
@@ -15435,7 +15432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -15449,7 +15446,7 @@
         <v>-1</v>
       </c>
       <c r="E171" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F171">
         <v>16</v>
@@ -15473,7 +15470,7 @@
         <v>63</v>
       </c>
       <c r="M171" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N171" t="s">
         <v>28</v>
@@ -15488,7 +15485,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -15502,7 +15499,7 @@
         <v>-1</v>
       </c>
       <c r="E172" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F172">
         <v>16</v>
@@ -15526,7 +15523,7 @@
         <v>63</v>
       </c>
       <c r="M172" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N172" t="s">
         <v>28</v>
@@ -15541,7 +15538,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -15555,7 +15552,7 @@
         <v>-1</v>
       </c>
       <c r="E173" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F173">
         <v>16</v>
@@ -15594,7 +15591,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>18</v>
       </c>
@@ -15608,7 +15605,7 @@
         <v>-1</v>
       </c>
       <c r="E174" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F174">
         <v>16</v>
@@ -15626,10 +15623,10 @@
         <v>24</v>
       </c>
       <c r="K174" t="s">
+        <v>69</v>
+      </c>
+      <c r="L174" t="s">
         <v>70</v>
-      </c>
-      <c r="L174" t="s">
-        <v>71</v>
       </c>
       <c r="M174" t="s">
         <v>32</v>
@@ -15647,7 +15644,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>18</v>
       </c>
@@ -15661,7 +15658,7 @@
         <v>-1</v>
       </c>
       <c r="E175" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F175">
         <v>16</v>
@@ -15700,7 +15697,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>18</v>
       </c>
@@ -15714,7 +15711,7 @@
         <v>-1</v>
       </c>
       <c r="E176" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F176">
         <v>16</v>
@@ -15753,7 +15750,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>18</v>
       </c>
@@ -15767,7 +15764,7 @@
         <v>-1</v>
       </c>
       <c r="E177" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F177">
         <v>16</v>
@@ -15806,7 +15803,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>18</v>
       </c>
@@ -15820,7 +15817,7 @@
         <v>-1</v>
       </c>
       <c r="E178" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F178">
         <v>16</v>
@@ -15859,7 +15856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -15873,7 +15870,7 @@
         <v>-1</v>
       </c>
       <c r="E179" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F179">
         <v>16</v>
@@ -15891,10 +15888,10 @@
         <v>24</v>
       </c>
       <c r="K179" t="s">
+        <v>72</v>
+      </c>
+      <c r="L179" t="s">
         <v>73</v>
-      </c>
-      <c r="L179" t="s">
-        <v>74</v>
       </c>
       <c r="M179" t="s">
         <v>35</v>
@@ -15912,7 +15909,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -15926,7 +15923,7 @@
         <v>-1</v>
       </c>
       <c r="E180" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F180">
         <v>16</v>
@@ -15965,7 +15962,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -15979,7 +15976,7 @@
         <v>-1</v>
       </c>
       <c r="E181" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F181">
         <v>16</v>
@@ -16003,7 +16000,7 @@
         <v>63</v>
       </c>
       <c r="M181" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N181" t="s">
         <v>28</v>
@@ -16018,7 +16015,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -16032,7 +16029,7 @@
         <v>-1</v>
       </c>
       <c r="E182" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F182">
         <v>16</v>
@@ -16071,7 +16068,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -16085,7 +16082,7 @@
         <v>-1</v>
       </c>
       <c r="E183" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F183">
         <v>16</v>
@@ -16124,7 +16121,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -16138,7 +16135,7 @@
         <v>-1</v>
       </c>
       <c r="E184" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F184">
         <v>16</v>
@@ -16162,7 +16159,7 @@
         <v>63</v>
       </c>
       <c r="M184" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N184" t="s">
         <v>28</v>
@@ -16177,7 +16174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -16191,7 +16188,7 @@
         <v>-1</v>
       </c>
       <c r="E185" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F185">
         <v>16</v>
@@ -16230,7 +16227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -16244,7 +16241,7 @@
         <v>-1</v>
       </c>
       <c r="E186" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F186">
         <v>16</v>
@@ -16283,7 +16280,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -16297,7 +16294,7 @@
         <v>-1</v>
       </c>
       <c r="E187" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F187">
         <v>16</v>
@@ -16336,7 +16333,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -16350,7 +16347,7 @@
         <v>-1</v>
       </c>
       <c r="E188" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F188">
         <v>16</v>
@@ -16389,7 +16386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -16403,7 +16400,7 @@
         <v>-1</v>
       </c>
       <c r="E189" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F189">
         <v>16</v>
@@ -16442,7 +16439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -16456,7 +16453,7 @@
         <v>-1</v>
       </c>
       <c r="E190" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F190">
         <v>16</v>
@@ -16495,7 +16492,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -16509,7 +16506,7 @@
         <v>-1</v>
       </c>
       <c r="E191" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F191">
         <v>16</v>
@@ -16548,7 +16545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -16562,7 +16559,7 @@
         <v>-1</v>
       </c>
       <c r="E192" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F192">
         <v>16</v>
@@ -16601,7 +16598,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -16615,7 +16612,7 @@
         <v>-1</v>
       </c>
       <c r="E193" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F193">
         <v>16</v>
@@ -16639,7 +16636,7 @@
         <v>63</v>
       </c>
       <c r="M193" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N193" t="s">
         <v>28</v>
@@ -16654,7 +16651,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>18</v>
       </c>
@@ -16668,7 +16665,7 @@
         <v>-1</v>
       </c>
       <c r="E194" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F194">
         <v>16</v>
@@ -16707,7 +16704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -16721,7 +16718,7 @@
         <v>-1</v>
       </c>
       <c r="E195" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F195">
         <v>16</v>
@@ -16760,7 +16757,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -16774,7 +16771,7 @@
         <v>-1</v>
       </c>
       <c r="E196" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F196">
         <v>16</v>
@@ -16813,7 +16810,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -16827,7 +16824,7 @@
         <v>-1</v>
       </c>
       <c r="E197" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F197">
         <v>16</v>
@@ -16851,7 +16848,7 @@
         <v>63</v>
       </c>
       <c r="M197" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N197" t="s">
         <v>28</v>
@@ -16866,7 +16863,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -16880,7 +16877,7 @@
         <v>-1</v>
       </c>
       <c r="E198" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F198">
         <v>16</v>
@@ -16919,7 +16916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -16933,7 +16930,7 @@
         <v>-1</v>
       </c>
       <c r="E199" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F199">
         <v>16</v>
@@ -16972,7 +16969,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -16986,7 +16983,7 @@
         <v>-1</v>
       </c>
       <c r="E200" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F200">
         <v>16</v>
@@ -17025,7 +17022,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -17039,7 +17036,7 @@
         <v>-1</v>
       </c>
       <c r="E201" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F201">
         <v>16</v>
@@ -17063,7 +17060,7 @@
         <v>63</v>
       </c>
       <c r="M201" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N201" t="s">
         <v>28</v>
@@ -17078,7 +17075,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -17092,7 +17089,7 @@
         <v>-1</v>
       </c>
       <c r="E202" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F202">
         <v>16</v>
@@ -17131,7 +17128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -17145,7 +17142,7 @@
         <v>-1</v>
       </c>
       <c r="E203" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F203">
         <v>16</v>
@@ -17184,7 +17181,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -17198,7 +17195,7 @@
         <v>-1</v>
       </c>
       <c r="E204" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F204">
         <v>16</v>
@@ -17216,10 +17213,10 @@
         <v>24</v>
       </c>
       <c r="K204" t="s">
+        <v>69</v>
+      </c>
+      <c r="L204" t="s">
         <v>70</v>
-      </c>
-      <c r="L204" t="s">
-        <v>71</v>
       </c>
       <c r="M204" t="s">
         <v>32</v>
@@ -17237,7 +17234,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -17251,7 +17248,7 @@
         <v>-1</v>
       </c>
       <c r="E205" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F205">
         <v>16</v>
@@ -17275,7 +17272,7 @@
         <v>63</v>
       </c>
       <c r="M205" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N205" t="s">
         <v>28</v>
@@ -17290,7 +17287,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -17304,7 +17301,7 @@
         <v>-1</v>
       </c>
       <c r="E206" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F206">
         <v>16</v>
@@ -17343,7 +17340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -17357,7 +17354,7 @@
         <v>-1</v>
       </c>
       <c r="E207" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F207">
         <v>16</v>
@@ -17396,7 +17393,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:17" ht="30" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>18</v>
       </c>
@@ -17410,7 +17407,7 @@
         <v>-1</v>
       </c>
       <c r="E208" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F208">
         <v>16</v>
@@ -17434,7 +17431,7 @@
         <v>63</v>
       </c>
       <c r="M208" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N208" t="s">
         <v>28</v>
@@ -17449,7 +17446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -17463,7 +17460,7 @@
         <v>-1</v>
       </c>
       <c r="E209" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F209">
         <v>16</v>
@@ -17502,7 +17499,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -17516,7 +17513,7 @@
         <v>-1</v>
       </c>
       <c r="E210" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F210">
         <v>16</v>
@@ -17555,7 +17552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -17569,7 +17566,7 @@
         <v>-1</v>
       </c>
       <c r="E211" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F211">
         <v>16</v>
@@ -17608,7 +17605,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -17622,7 +17619,7 @@
         <v>-1</v>
       </c>
       <c r="E212" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F212">
         <v>16</v>
@@ -17640,10 +17637,10 @@
         <v>24</v>
       </c>
       <c r="K212" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L212" s="3" t="s">
         <v>67</v>
-      </c>
-      <c r="L212" s="3" t="s">
-        <v>68</v>
       </c>
       <c r="M212" s="4" t="s">
         <v>57</v>
@@ -17661,10 +17658,10 @@
         <v>1</v>
       </c>
       <c r="R212" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.25">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -17678,7 +17675,7 @@
         <v>-1</v>
       </c>
       <c r="E213" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F213">
         <v>16</v>
@@ -17717,7 +17714,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -17731,7 +17728,7 @@
         <v>-1</v>
       </c>
       <c r="E214" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F214">
         <v>16</v>
@@ -17770,10 +17767,10 @@
         <v>1</v>
       </c>
       <c r="R214" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -17787,7 +17784,7 @@
         <v>-1</v>
       </c>
       <c r="E215" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F215">
         <v>16</v>
@@ -17826,7 +17823,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -17840,7 +17837,7 @@
         <v>-1</v>
       </c>
       <c r="E216" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F216">
         <v>16</v>
@@ -17879,7 +17876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -17893,7 +17890,7 @@
         <v>-1</v>
       </c>
       <c r="E217" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F217">
         <v>16</v>
@@ -17932,7 +17929,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -17946,7 +17943,7 @@
         <v>-1</v>
       </c>
       <c r="E218" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F218">
         <v>16</v>
@@ -17985,10 +17982,10 @@
         <v>1</v>
       </c>
       <c r="R218" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -18002,7 +17999,7 @@
         <v>-1</v>
       </c>
       <c r="E219" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F219">
         <v>16</v>
@@ -18041,7 +18038,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -18055,7 +18052,7 @@
         <v>-1</v>
       </c>
       <c r="E220" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F220">
         <v>16</v>
@@ -18094,7 +18091,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -18108,7 +18105,7 @@
         <v>-1</v>
       </c>
       <c r="E221" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F221">
         <v>16</v>
@@ -18147,7 +18144,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -18161,7 +18158,7 @@
         <v>-1</v>
       </c>
       <c r="E222" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F222">
         <v>16</v>
@@ -18200,7 +18197,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -18214,7 +18211,7 @@
         <v>-1</v>
       </c>
       <c r="E223" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F223">
         <v>16</v>
@@ -18232,10 +18229,10 @@
         <v>24</v>
       </c>
       <c r="K223" t="s">
+        <v>72</v>
+      </c>
+      <c r="L223" t="s">
         <v>73</v>
-      </c>
-      <c r="L223" t="s">
-        <v>74</v>
       </c>
       <c r="M223" t="s">
         <v>35</v>
@@ -18253,7 +18250,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -18267,7 +18264,7 @@
         <v>-1</v>
       </c>
       <c r="E224" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F224">
         <v>16</v>
@@ -18306,7 +18303,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -18320,7 +18317,7 @@
         <v>-1</v>
       </c>
       <c r="E225" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F225">
         <v>16</v>
@@ -18359,7 +18356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -18373,7 +18370,7 @@
         <v>-1</v>
       </c>
       <c r="E226" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F226">
         <v>16</v>
@@ -18391,10 +18388,10 @@
         <v>24</v>
       </c>
       <c r="K226" t="s">
+        <v>72</v>
+      </c>
+      <c r="L226" t="s">
         <v>73</v>
-      </c>
-      <c r="L226" t="s">
-        <v>74</v>
       </c>
       <c r="M226" t="s">
         <v>35</v>
@@ -18412,7 +18409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>18</v>
       </c>
@@ -18426,7 +18423,7 @@
         <v>-1</v>
       </c>
       <c r="E227" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F227">
         <v>16</v>
@@ -18465,7 +18462,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -18479,7 +18476,7 @@
         <v>-1</v>
       </c>
       <c r="E228" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F228">
         <v>16</v>
@@ -18518,10 +18515,10 @@
         <v>1</v>
       </c>
       <c r="R228" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -18535,7 +18532,7 @@
         <v>-1</v>
       </c>
       <c r="E229" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F229">
         <v>16</v>
@@ -18574,7 +18571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -18588,7 +18585,7 @@
         <v>-1</v>
       </c>
       <c r="E230" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F230">
         <v>16</v>
@@ -18606,10 +18603,10 @@
         <v>24</v>
       </c>
       <c r="K230" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L230" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="L230" s="2" t="s">
-        <v>78</v>
       </c>
       <c r="M230" t="s">
         <v>52</v>
@@ -18627,7 +18624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -18641,7 +18638,7 @@
         <v>-1</v>
       </c>
       <c r="E231" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F231">
         <v>16</v>
@@ -18680,7 +18677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -18694,7 +18691,7 @@
         <v>-1</v>
       </c>
       <c r="E232" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F232">
         <v>16</v>
@@ -18733,7 +18730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -18747,7 +18744,7 @@
         <v>-1</v>
       </c>
       <c r="E233" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F233">
         <v>16</v>
@@ -18786,7 +18783,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -18800,7 +18797,7 @@
         <v>-1</v>
       </c>
       <c r="E234" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F234">
         <v>16</v>
@@ -18839,7 +18836,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -18853,7 +18850,7 @@
         <v>-1</v>
       </c>
       <c r="E235" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F235">
         <v>16</v>
@@ -18892,7 +18889,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -18906,7 +18903,7 @@
         <v>-1</v>
       </c>
       <c r="E236" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F236">
         <v>16</v>
@@ -18945,7 +18942,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -18959,7 +18956,7 @@
         <v>-1</v>
       </c>
       <c r="E237" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F237">
         <v>16</v>
@@ -18998,7 +18995,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="238" spans="1:18" ht="30" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -19012,7 +19009,7 @@
         <v>-1</v>
       </c>
       <c r="E238" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F238">
         <v>16</v>
@@ -19036,7 +19033,7 @@
         <v>63</v>
       </c>
       <c r="M238" s="4" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N238" t="s">
         <v>28</v>
@@ -19051,7 +19048,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -19065,7 +19062,7 @@
         <v>-1</v>
       </c>
       <c r="E239" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F239">
         <v>8</v>
@@ -19083,10 +19080,10 @@
         <v>24</v>
       </c>
       <c r="K239" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="L239" s="3" t="s">
         <v>80</v>
-      </c>
-      <c r="L239" s="3" t="s">
-        <v>81</v>
       </c>
       <c r="M239" s="4" t="s">
         <v>35</v>
@@ -19104,7 +19101,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -19118,7 +19115,7 @@
         <v>-1</v>
       </c>
       <c r="E240" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F240">
         <v>8</v>
@@ -19136,10 +19133,10 @@
         <v>24</v>
       </c>
       <c r="K240" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L240" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="L240" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="M240" s="4" t="s">
         <v>39</v>
@@ -19157,7 +19154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A241" s="6" t="s">
         <v>18</v>
       </c>
@@ -19171,7 +19168,7 @@
         <v>-1</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F241" s="6">
         <v>16</v>
@@ -19189,10 +19186,10 @@
         <v>24</v>
       </c>
       <c r="K241" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="L241" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="L241" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="M241" s="6" t="s">
         <v>52</v>
@@ -19210,7 +19207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="242" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A242" s="6" t="s">
         <v>18</v>
       </c>
@@ -19224,7 +19221,7 @@
         <v>-1</v>
       </c>
       <c r="E242" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F242" s="6">
         <v>16</v>
@@ -19263,7 +19260,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="243" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A243" s="6" t="s">
         <v>18</v>
       </c>
@@ -19295,10 +19292,10 @@
         <v>24</v>
       </c>
       <c r="K243" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L243" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="L243" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="M243" s="9" t="s">
         <v>35</v>
@@ -19316,7 +19313,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="244" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A244" s="6" t="s">
         <v>18</v>
       </c>
@@ -19330,7 +19327,7 @@
         <v>-1</v>
       </c>
       <c r="E244" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F244" s="6">
         <v>16</v>
@@ -19348,10 +19345,10 @@
         <v>24</v>
       </c>
       <c r="K244" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="L244" s="8" t="s">
         <v>80</v>
-      </c>
-      <c r="L244" s="8" t="s">
-        <v>81</v>
       </c>
       <c r="M244" s="9" t="s">
         <v>35</v>
@@ -19369,7 +19366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="245" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A245" s="6" t="s">
         <v>18</v>
       </c>
@@ -19383,7 +19380,7 @@
         <v>-1</v>
       </c>
       <c r="E245" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F245" s="6">
         <v>16</v>
@@ -19401,10 +19398,10 @@
         <v>24</v>
       </c>
       <c r="K245" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="L245" s="8" t="s">
         <v>65</v>
-      </c>
-      <c r="L245" s="8" t="s">
-        <v>66</v>
       </c>
       <c r="M245" s="9" t="s">
         <v>39</v>
@@ -19422,7 +19419,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="246" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A246" s="6" t="s">
         <v>18</v>
       </c>
@@ -19454,10 +19451,10 @@
         <v>24</v>
       </c>
       <c r="K246" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="L246" s="6" t="s">
         <v>77</v>
-      </c>
-      <c r="L246" s="6" t="s">
-        <v>78</v>
       </c>
       <c r="M246" s="6" t="s">
         <v>52</v>
